--- a/research/traditional_assets/database/data/japan/japan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0168</v>
+        <v>0.007209999999999999</v>
       </c>
       <c r="E2">
-        <v>0.028225</v>
+        <v>-0.0315</v>
       </c>
       <c r="F2">
-        <v>0.0883</v>
+        <v>0.0616</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.001468350906977558</v>
+        <v>0.004130894893485851</v>
       </c>
       <c r="J2">
-        <v>0.001098162236964857</v>
+        <v>0.003302001053611397</v>
       </c>
       <c r="K2">
-        <v>29111.4</v>
+        <v>2187.8</v>
       </c>
       <c r="L2">
-        <v>0.2481458150955073</v>
+        <v>0.03594961335844121</v>
       </c>
       <c r="M2">
-        <v>9249.1098</v>
+        <v>8525.089</v>
       </c>
       <c r="N2">
-        <v>0.04665746442467322</v>
+        <v>0.05112586065964565</v>
       </c>
       <c r="O2">
-        <v>0.3177143593231517</v>
+        <v>3.896649145260079</v>
       </c>
       <c r="P2">
-        <v>7932.5628</v>
+        <v>5609.749</v>
       </c>
       <c r="Q2">
-        <v>0.04001609610445821</v>
+        <v>0.0336422582461704</v>
       </c>
       <c r="R2">
-        <v>0.2724899111688204</v>
+        <v>2.564105037023494</v>
       </c>
       <c r="S2">
-        <v>1316.547</v>
+        <v>2915.34</v>
       </c>
       <c r="T2">
-        <v>0.1423431041979845</v>
+        <v>0.3419717964234743</v>
       </c>
       <c r="U2">
-        <v>2650475.4</v>
+        <v>1632853.6</v>
       </c>
       <c r="V2">
-        <v>13.3704177329554</v>
+        <v>9.792395789791847</v>
       </c>
       <c r="W2">
-        <v>0.06736240662403878</v>
+        <v>0.03875577688403133</v>
       </c>
       <c r="X2">
-        <v>0.2415363501573652</v>
+        <v>0.2531494847067445</v>
       </c>
       <c r="Y2">
-        <v>-0.1741739435333265</v>
+        <v>-0.2143937078227132</v>
       </c>
       <c r="Z2">
-        <v>-2.111914582613634</v>
+        <v>0.592321106848397</v>
       </c>
       <c r="AA2">
-        <v>-3.766622877246534e-06</v>
+        <v>0.02919432221351488</v>
       </c>
       <c r="AB2">
-        <v>0.04281301159410882</v>
+        <v>0.0728246364000876</v>
       </c>
       <c r="AC2">
-        <v>-0.04229893486927638</v>
+        <v>-0.03833443353566245</v>
       </c>
       <c r="AD2">
-        <v>1980508.4</v>
+        <v>1228260.1</v>
       </c>
       <c r="AE2">
-        <v>6568.146927511464</v>
+        <v>4513.122385545871</v>
       </c>
       <c r="AF2">
-        <v>1987076.546927511</v>
+        <v>1232773.222385546</v>
       </c>
       <c r="AG2">
-        <v>-663398.8530724884</v>
+        <v>-400080.3776144541</v>
       </c>
       <c r="AH2">
-        <v>0.9092878249889657</v>
+        <v>0.8808541059869912</v>
       </c>
       <c r="AI2">
-        <v>0.7995867697527425</v>
+        <v>0.8186321785751425</v>
       </c>
       <c r="AJ2">
-        <v>1.426159514285063</v>
+        <v>1.714630599221783</v>
       </c>
       <c r="AK2">
-        <v>4.012184389921006</v>
+        <v>3.151239709582452</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>1332.876861678859</v>
+        <v>1064.331727353079</v>
       </c>
       <c r="AP2">
-        <v>-446.4656556491317</v>
+        <v>-346.6840935291019</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sumitomo Mitsui Trust Holdings, Inc. (TSE:8309)</t>
+          <t>Mitsubishi UFJ Financial Group, Inc. (TSE:8306)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0166</v>
+        <v>0.0188</v>
       </c>
       <c r="E3">
-        <v>0.00505</v>
+        <v>0.122</v>
       </c>
       <c r="F3">
-        <v>0.143</v>
+        <v>0.0751</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,91 +734,82 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.000215799730817956</v>
+        <v>0.008355877141823096</v>
       </c>
       <c r="J3">
-        <v>0.0001577195993650571</v>
+        <v>0.008355877141823096</v>
       </c>
       <c r="K3">
-        <v>1552.2</v>
+        <v>-4379.5</v>
       </c>
       <c r="L3">
-        <v>0.1547819670332958</v>
+        <v>-0.1761537780852553</v>
       </c>
       <c r="M3">
-        <v>520.891</v>
+        <v>4999</v>
       </c>
       <c r="N3">
-        <v>0.04166494692806693</v>
+        <v>0.05938112490348637</v>
       </c>
       <c r="O3">
-        <v>0.335582399175364</v>
+        <v>-1.141454503938806</v>
       </c>
       <c r="P3">
-        <v>520.694</v>
+        <v>2307.4</v>
       </c>
       <c r="Q3">
-        <v>0.04164918932322287</v>
+        <v>0.02740868325711231</v>
       </c>
       <c r="R3">
-        <v>0.3354554825409096</v>
+        <v>-0.5268637972371275</v>
       </c>
       <c r="S3">
-        <v>0.1970000000000027</v>
+        <v>2691.6</v>
       </c>
       <c r="T3">
-        <v>0.0003781981259035052</v>
+        <v>0.5384276855371074</v>
       </c>
       <c r="U3">
-        <v>169506.1</v>
+        <v>707587.1</v>
       </c>
       <c r="V3">
-        <v>13.5584271190779</v>
+        <v>8.405144621963533</v>
       </c>
       <c r="W3">
-        <v>0.06288411286892054</v>
+        <v>-0.02744413884810441</v>
       </c>
       <c r="X3">
-        <v>0.2662178536670807</v>
+        <v>0.2531494847067445</v>
       </c>
       <c r="Y3">
-        <v>-0.2033337407981602</v>
-      </c>
-      <c r="Z3">
-        <v>-1.777178622028052</v>
-      </c>
-      <c r="AA3">
-        <v>-0.0002802959002664086</v>
+        <v>-0.2805936235548489</v>
       </c>
       <c r="AB3">
-        <v>0.03986352167188578</v>
-      </c>
-      <c r="AC3">
-        <v>-0.04014381757215219</v>
+        <v>0.0728246364000876</v>
       </c>
       <c r="AD3">
-        <v>144865.5</v>
+        <v>631009.7</v>
       </c>
       <c r="AE3">
-        <v>166.6794777971915</v>
+        <v>2626.289268377113</v>
       </c>
       <c r="AF3">
-        <v>145032.1794777972</v>
+        <v>633635.9892683771</v>
       </c>
       <c r="AG3">
-        <v>-24473.92052220282</v>
+        <v>-73951.1107316229</v>
       </c>
       <c r="AH3">
-        <v>0.9206400288658683</v>
+        <v>0.8827214566603804</v>
       </c>
       <c r="AI3">
-        <v>0.8527864460509088</v>
+        <v>0.8370221751392957</v>
       </c>
       <c r="AJ3">
-        <v>2.044259820371547</v>
+        <v>-7.226100340965499</v>
       </c>
       <c r="AK3">
-        <v>-43.51077948310113</v>
+        <v>-1.496226143974573</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -827,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>4080.718309859155</v>
+        <v>860.8590723055934</v>
       </c>
       <c r="AP3">
-        <v>-689.4062118930373</v>
+        <v>-100.8882820349562</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mitsubishi UFJ Financial Group, Inc. (TSE:8306)</t>
+          <t>JAPAN POST BANK Co., Ltd. (TSE:7182)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,13 +841,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0222</v>
+        <v>-0.0184</v>
       </c>
       <c r="E4">
-        <v>0.101</v>
-      </c>
-      <c r="F4">
-        <v>0.0956</v>
+        <v>-0.0408</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,91 +853,82 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.004001842782409895</v>
+        <v>0.0001489874687723761</v>
       </c>
       <c r="J4">
-        <v>0.003198980902577378</v>
+        <v>0.0001083270855589974</v>
       </c>
       <c r="K4">
-        <v>10057.4</v>
+        <v>1924.1</v>
       </c>
       <c r="L4">
-        <v>0.2422104162953901</v>
+        <v>0.1937019922885647</v>
       </c>
       <c r="M4">
-        <v>1515.7</v>
+        <v>1303.568</v>
       </c>
       <c r="N4">
-        <v>0.02175023605686028</v>
+        <v>0.04066114980676434</v>
       </c>
       <c r="O4">
-        <v>0.1507049535665281</v>
+        <v>0.6774949326958059</v>
       </c>
       <c r="P4">
-        <v>1439.3</v>
+        <v>1296.808</v>
       </c>
       <c r="Q4">
-        <v>0.02065389902793363</v>
+        <v>0.04045029055531468</v>
       </c>
       <c r="R4">
-        <v>0.1431085568834888</v>
+        <v>0.6739816017878489</v>
       </c>
       <c r="S4">
-        <v>76.40000000000009</v>
+        <v>6.759999999999991</v>
       </c>
       <c r="T4">
-        <v>0.05040575311737157</v>
+        <v>0.005185767063935284</v>
       </c>
       <c r="U4">
-        <v>937669.5</v>
+        <v>416112.2</v>
       </c>
       <c r="V4">
-        <v>13.45552086053847</v>
+        <v>12.97945369986244</v>
       </c>
       <c r="W4">
-        <v>0.06969080051498601</v>
+        <v>0.01874329065981916</v>
       </c>
       <c r="X4">
-        <v>0.2546469723312966</v>
+        <v>0.173005325020786</v>
       </c>
       <c r="Y4">
-        <v>-0.1849561718163106</v>
-      </c>
-      <c r="Z4">
-        <v>0.2748493411005017</v>
-      </c>
-      <c r="AA4">
-        <v>0.0008792377932664804</v>
+        <v>-0.1542620343609668</v>
       </c>
       <c r="AB4">
-        <v>0.04281327809153839</v>
-      </c>
-      <c r="AC4">
-        <v>-0.04193404029827191</v>
+        <v>0.07138013236486049</v>
       </c>
       <c r="AD4">
-        <v>762562.8</v>
+        <v>135468.3</v>
       </c>
       <c r="AE4">
-        <v>3980.149407044405</v>
+        <v>3.700313882216781</v>
       </c>
       <c r="AF4">
-        <v>766542.9494070444</v>
+        <v>135472.0003138822</v>
       </c>
       <c r="AG4">
-        <v>-171126.5505929556</v>
+        <v>-280640.1996861178</v>
       </c>
       <c r="AH4">
-        <v>0.9166657049497791</v>
+        <v>0.8086369535726485</v>
       </c>
       <c r="AI4">
-        <v>0.8201594378647546</v>
+        <v>0.6740286140864608</v>
       </c>
       <c r="AJ4">
-        <v>1.686973915036975</v>
+        <v>1.128969281390811</v>
       </c>
       <c r="AK4">
-        <v>56.24074184362659</v>
+        <v>1.304552683389109</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -958,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>792.5200581999584</v>
+        <v>61021.75675675675</v>
       </c>
       <c r="AP4">
-        <v>-177.84925233107</v>
+        <v>-126414.5043631161</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JAPAN POST BANK Co.,Ltd. (TSE:7182)</t>
+          <t>Sumitomo Mitsui Trust Holdings, Inc. (TSE:8309)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,13 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.017</v>
+        <v>0.00868</v>
       </c>
       <c r="E5">
-        <v>0.05139999999999999</v>
-      </c>
-      <c r="F5">
-        <v>0.008319999999999999</v>
+        <v>0.0827</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -996,91 +972,91 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.0001586738948313327</v>
+        <v>0.001325548977612136</v>
       </c>
       <c r="J5">
-        <v>0.0001122940222559874</v>
+        <v>0.0009796064644394197</v>
       </c>
       <c r="K5">
-        <v>3507.4</v>
+        <v>1120.2</v>
       </c>
       <c r="L5">
-        <v>0.2324074319488987</v>
+        <v>0.1447342920268228</v>
       </c>
       <c r="M5">
-        <v>1680.8988</v>
+        <v>679.4930000000001</v>
       </c>
       <c r="N5">
-        <v>0.04894514959598165</v>
+        <v>0.05420030789601729</v>
       </c>
       <c r="O5">
-        <v>0.4792435422250099</v>
+        <v>0.6065818603820746</v>
       </c>
       <c r="P5">
-        <v>1679.1488</v>
+        <v>471.9930000000001</v>
       </c>
       <c r="Q5">
-        <v>0.04889419232729125</v>
+        <v>0.03764890282131662</v>
       </c>
       <c r="R5">
-        <v>0.4787445971374807</v>
+        <v>0.4213470808784146</v>
       </c>
       <c r="S5">
-        <v>1.75</v>
+        <v>207.5</v>
       </c>
       <c r="T5">
-        <v>0.001041109672991616</v>
+        <v>0.305374742638997</v>
       </c>
       <c r="U5">
-        <v>547282.6</v>
+        <v>136002.9</v>
       </c>
       <c r="V5">
-        <v>15.93601514158841</v>
+        <v>10.84838115293498</v>
       </c>
       <c r="W5">
-        <v>0.03346123537728559</v>
+        <v>0.04519286241633753</v>
       </c>
       <c r="X5">
-        <v>0.1502198611460435</v>
+        <v>0.3059520170908939</v>
       </c>
       <c r="Y5">
-        <v>-0.116758625768758</v>
+        <v>-0.2607591546745563</v>
       </c>
       <c r="Z5">
-        <v>-0.06708501132250969</v>
+        <v>29.80209224141997</v>
       </c>
       <c r="AA5">
-        <v>-7.533245754493068e-06</v>
+        <v>0.02919432221351488</v>
       </c>
       <c r="AB5">
-        <v>0.04194296690947045</v>
+        <v>0.06752875574917733</v>
       </c>
       <c r="AC5">
-        <v>-0.04195050015522494</v>
+        <v>-0.03833443353566245</v>
       </c>
       <c r="AD5">
-        <v>191500.5</v>
+        <v>121512.6</v>
       </c>
       <c r="AE5">
-        <v>3.4767852438173</v>
+        <v>113.2032428898767</v>
       </c>
       <c r="AF5">
-        <v>191503.9767852438</v>
+        <v>121625.8032428899</v>
       </c>
       <c r="AG5">
-        <v>-355778.6232147561</v>
+        <v>-14377.09675711011</v>
       </c>
       <c r="AH5">
-        <v>0.8479387392318893</v>
+        <v>0.9065558580305902</v>
       </c>
       <c r="AI5">
-        <v>0.6504409384259984</v>
+        <v>0.8647660574431875</v>
       </c>
       <c r="AJ5">
-        <v>1.106840823167393</v>
+        <v>7.811955058911227</v>
       </c>
       <c r="AK5">
-        <v>1.407013623904053</v>
+        <v>-3.096508015394263</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1089,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>61974.27184466019</v>
+        <v>3693.392097264438</v>
       </c>
       <c r="AP5">
-        <v>-115138.7130144842</v>
+        <v>-436.9938224045625</v>
       </c>
     </row>
     <row r="6">
@@ -1112,13 +1088,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0175</v>
+        <v>0.007209999999999999</v>
       </c>
       <c r="E6">
-        <v>-0.0588</v>
+        <v>-0.0555</v>
       </c>
       <c r="F6">
-        <v>0.0699</v>
+        <v>0.0143</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1127,34 +1103,34 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.007153916528038892</v>
+        <v>0.00941093275580126</v>
       </c>
       <c r="J6">
-        <v>0.004846756925735134</v>
+        <v>0.006764320258772675</v>
       </c>
       <c r="K6">
-        <v>298.4</v>
+        <v>213.9</v>
       </c>
       <c r="L6">
-        <v>0.2760151697345297</v>
+        <v>0.2569369369369369</v>
       </c>
       <c r="M6">
-        <v>134.32</v>
+        <v>129.648</v>
       </c>
       <c r="N6">
-        <v>0.05259819086032032</v>
+        <v>0.0564177545691906</v>
       </c>
       <c r="O6">
-        <v>0.4501340482573727</v>
+        <v>0.6061150070126227</v>
       </c>
       <c r="P6">
-        <v>134.32</v>
+        <v>129.648</v>
       </c>
       <c r="Q6">
-        <v>0.05259819086032032</v>
+        <v>0.0564177545691906</v>
       </c>
       <c r="R6">
-        <v>0.4501340482573727</v>
+        <v>0.6061150070126227</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1163,55 +1139,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>8447.5</v>
+        <v>6711.5</v>
       </c>
       <c r="V6">
-        <v>3.307945334220935</v>
+        <v>2.920583115752828</v>
       </c>
       <c r="W6">
-        <v>0.06585597316324954</v>
+        <v>0.0457510747973392</v>
       </c>
       <c r="X6">
-        <v>0.1055809064673202</v>
+        <v>0.1422752058348026</v>
       </c>
       <c r="Y6">
-        <v>-0.03972493330407065</v>
+        <v>-0.09652413103746341</v>
       </c>
       <c r="Z6">
-        <v>0.15998213564784</v>
+        <v>0.1820855391674471</v>
       </c>
       <c r="AA6">
-        <v>0.0007753945239450661</v>
+        <v>0.001231684901419908</v>
       </c>
       <c r="AB6">
-        <v>0.0434227641072729</v>
+        <v>0.07354576888970157</v>
       </c>
       <c r="AC6">
-        <v>-0.04264736958332783</v>
+        <v>-0.07231408398828167</v>
       </c>
       <c r="AD6">
-        <v>8296.4</v>
+        <v>6754.1</v>
       </c>
       <c r="AE6">
-        <v>23.32950420768578</v>
+        <v>47.82699240397725</v>
       </c>
       <c r="AF6">
-        <v>8319.729504207686</v>
+        <v>6801.926992403977</v>
       </c>
       <c r="AG6">
-        <v>-127.7704957923143</v>
+        <v>90.42699240397724</v>
       </c>
       <c r="AH6">
-        <v>0.765143095008636</v>
+        <v>0.7474705014756471</v>
       </c>
       <c r="AI6">
-        <v>0.64246357435531</v>
+        <v>0.6916866645770812</v>
       </c>
       <c r="AJ6">
-        <v>-0.05266867630353686</v>
+        <v>0.03786048001113967</v>
       </c>
       <c r="AK6">
-        <v>-0.02837938307518591</v>
+        <v>0.02896141007138867</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1220,10 +1196,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>669.0645161290322</v>
+        <v>388.1666666666667</v>
       </c>
       <c r="AP6">
-        <v>-10.30407224131567</v>
+        <v>5.196953586435474</v>
       </c>
     </row>
     <row r="7">
@@ -1234,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sumitomo Mitsui Financial Group, Inc. (TSE:8316)</t>
+          <t>Mizuho Financial Group, Inc. (TSE:8411)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1243,13 +1219,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0645</v>
+        <v>-0.0147</v>
       </c>
       <c r="E7">
-        <v>0.07490000000000001</v>
+        <v>-0.0315</v>
       </c>
       <c r="F7">
-        <v>0.164</v>
+        <v>0.0616</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1258,91 +1234,91 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>0.001376749498371223</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>0.001117691200573064</v>
       </c>
       <c r="K7">
-        <v>7948</v>
+        <v>3309.1</v>
       </c>
       <c r="L7">
-        <v>0.2898804443763631</v>
+        <v>0.1891984608435629</v>
       </c>
       <c r="M7">
-        <v>3670.4</v>
+        <v>1413.38</v>
       </c>
       <c r="N7">
-        <v>0.07818694228643124</v>
+        <v>0.03962588419343896</v>
       </c>
       <c r="O7">
-        <v>0.4618017111222948</v>
+        <v>0.4271191562660542</v>
       </c>
       <c r="P7">
-        <v>2451.7</v>
+        <v>1403.9</v>
       </c>
       <c r="Q7">
-        <v>0.05222616783011211</v>
+        <v>0.03936010048194325</v>
       </c>
       <c r="R7">
-        <v>0.3084675390035229</v>
+        <v>0.4242543289716237</v>
       </c>
       <c r="S7">
-        <v>1218.7</v>
+        <v>9.480000000000018</v>
       </c>
       <c r="T7">
-        <v>0.3320346556233653</v>
+        <v>0.006707325701509869</v>
       </c>
       <c r="U7">
-        <v>577539.7</v>
+        <v>366439.9</v>
       </c>
       <c r="V7">
-        <v>12.30276351134013</v>
+        <v>10.2736030234299</v>
       </c>
       <c r="W7">
-        <v>0.0746180378873369</v>
+        <v>0.03875577688403133</v>
       </c>
       <c r="X7">
-        <v>0.2284257279834339</v>
+        <v>0.2986010864311068</v>
       </c>
       <c r="Y7">
-        <v>-0.153807690096097</v>
+        <v>-0.2598453095470755</v>
       </c>
       <c r="Z7">
-        <v>-0.3687804563117116</v>
+        <v>0.1786304417761866</v>
       </c>
       <c r="AA7">
-        <v>-0</v>
+        <v>0.0001996536729277227</v>
       </c>
       <c r="AB7">
-        <v>0.04281372863442388</v>
+        <v>0.07288232993623946</v>
       </c>
       <c r="AC7">
-        <v>-0.04281372863442388</v>
+        <v>-0.07268267626331174</v>
       </c>
       <c r="AD7">
-        <v>452446.5</v>
+        <v>333515.4</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1722.102567992687</v>
       </c>
       <c r="AF7">
-        <v>452446.5</v>
+        <v>335237.5025679927</v>
       </c>
       <c r="AG7">
-        <v>-125093.2</v>
+        <v>-31202.3974320073</v>
       </c>
       <c r="AH7">
-        <v>0.9059975922644888</v>
+        <v>0.9038351004863523</v>
       </c>
       <c r="AI7">
-        <v>0.8030654280188136</v>
+        <v>0.8435483454934639</v>
       </c>
       <c r="AJ7">
-        <v>1.600695079802378</v>
+        <v>-6.987119486113151</v>
       </c>
       <c r="AK7">
-        <v>8.846510706910724</v>
+        <v>-1.007386769540688</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1350,136 +1326,11 @@
       <c r="AM7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Mizuho Financial Group, Inc. (TSE:8411)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>-0.013</v>
-      </c>
-      <c r="E8">
-        <v>-0.00117</v>
-      </c>
-      <c r="F8">
-        <v>0.081</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>-0.0002797241091084699</v>
-      </c>
-      <c r="J8">
-        <v>-0.0002382622120574746</v>
-      </c>
-      <c r="K8">
-        <v>5748</v>
-      </c>
-      <c r="L8">
-        <v>0.2592330346230342</v>
-      </c>
-      <c r="M8">
-        <v>1726.9</v>
-      </c>
-      <c r="N8">
-        <v>0.05362094287657154</v>
-      </c>
-      <c r="O8">
-        <v>0.3004349338900487</v>
-      </c>
-      <c r="P8">
-        <v>1707.4</v>
-      </c>
-      <c r="Q8">
-        <v>0.05301545999621185</v>
-      </c>
-      <c r="R8">
-        <v>0.2970424495476688</v>
-      </c>
-      <c r="S8">
-        <v>19.5</v>
-      </c>
-      <c r="T8">
-        <v>0.01129191035960391</v>
-      </c>
-      <c r="U8">
-        <v>410030</v>
-      </c>
-      <c r="V8">
-        <v>12.73159720173758</v>
-      </c>
-      <c r="W8">
-        <v>0.06886884008482801</v>
-      </c>
-      <c r="X8">
-        <v>0.2958827929821058</v>
-      </c>
-      <c r="Y8">
-        <v>-0.2270139528972778</v>
-      </c>
-      <c r="Z8">
-        <v>0.2421452707346969</v>
-      </c>
-      <c r="AA8">
-        <v>-5.769406784450495e-05</v>
-      </c>
-      <c r="AB8">
-        <v>0.04281274509667925</v>
-      </c>
-      <c r="AC8">
-        <v>-0.04287043916452375</v>
-      </c>
-      <c r="AD8">
-        <v>420836.7</v>
-      </c>
-      <c r="AE8">
-        <v>2394.511753218365</v>
-      </c>
-      <c r="AF8">
-        <v>423231.2117532184</v>
-      </c>
-      <c r="AG8">
-        <v>13201.21175321838</v>
-      </c>
-      <c r="AH8">
-        <v>0.9292861444277251</v>
-      </c>
-      <c r="AI8">
-        <v>0.8304135005101156</v>
-      </c>
-      <c r="AJ8">
-        <v>0.2907313279741535</v>
-      </c>
-      <c r="AK8">
-        <v>0.1324981050085635</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>890.2828432409563</v>
-      </c>
-      <c r="AP8">
-        <v>27.9272514347755</v>
+      <c r="AN7">
+        <v>905.062143826323</v>
+      </c>
+      <c r="AP7">
+        <v>-84.67407715605781</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/japan/japan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.007209999999999999</v>
+        <v>0.00127</v>
       </c>
       <c r="E2">
-        <v>-0.0315</v>
+        <v>0.005759999999999999</v>
       </c>
       <c r="F2">
-        <v>0.0616</v>
+        <v>0.128</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.004130894893485851</v>
+        <v>0.0036261209679027</v>
       </c>
       <c r="J2">
-        <v>0.003302001053611397</v>
+        <v>0.002843310271242587</v>
       </c>
       <c r="K2">
-        <v>2187.8</v>
+        <v>16550.7</v>
       </c>
       <c r="L2">
-        <v>0.03594961335844121</v>
+        <v>0.2470279540234002</v>
       </c>
       <c r="M2">
-        <v>8525.089</v>
+        <v>8549.968999999999</v>
       </c>
       <c r="N2">
-        <v>0.05112586065964565</v>
+        <v>0.04192581408702653</v>
       </c>
       <c r="O2">
-        <v>3.896649145260079</v>
+        <v>0.5165925912499169</v>
       </c>
       <c r="P2">
-        <v>5609.749</v>
+        <v>5983.569</v>
       </c>
       <c r="Q2">
-        <v>0.0336422582461704</v>
+        <v>0.02934115918676375</v>
       </c>
       <c r="R2">
-        <v>2.564105037023494</v>
+        <v>0.3615296633979227</v>
       </c>
       <c r="S2">
-        <v>2915.34</v>
+        <v>2566.4</v>
       </c>
       <c r="T2">
-        <v>0.3419717964234743</v>
+        <v>0.3001648310069897</v>
       </c>
       <c r="U2">
-        <v>1632853.6</v>
+        <v>1758012.9</v>
       </c>
       <c r="V2">
-        <v>9.792395789791847</v>
+        <v>8.620630321349045</v>
       </c>
       <c r="W2">
-        <v>0.03875577688403133</v>
+        <v>0.06918586739740243</v>
       </c>
       <c r="X2">
-        <v>0.2531494847067445</v>
+        <v>0.1526034413589269</v>
       </c>
       <c r="Y2">
-        <v>-0.2143937078227132</v>
+        <v>-0.08341757396152447</v>
       </c>
       <c r="Z2">
-        <v>0.592321106848397</v>
+        <v>0.8396296689759727</v>
       </c>
       <c r="AA2">
-        <v>0.02919432221351488</v>
+        <v>0.004829485916038289</v>
       </c>
       <c r="AB2">
-        <v>0.0728246364000876</v>
+        <v>0.05668749331717567</v>
       </c>
       <c r="AC2">
-        <v>-0.03833443353566245</v>
+        <v>-0.05185800740113738</v>
       </c>
       <c r="AD2">
-        <v>1228260.1</v>
+        <v>1344221.3</v>
       </c>
       <c r="AE2">
-        <v>4513.122385545871</v>
+        <v>3926.262167175983</v>
       </c>
       <c r="AF2">
-        <v>1232773.222385546</v>
+        <v>1348147.562167176</v>
       </c>
       <c r="AG2">
-        <v>-400080.3776144541</v>
+        <v>-409865.3378328241</v>
       </c>
       <c r="AH2">
-        <v>0.8808541059869912</v>
+        <v>0.8686078668244323</v>
       </c>
       <c r="AI2">
-        <v>0.8186321785751425</v>
+        <v>0.8269319127112789</v>
       </c>
       <c r="AJ2">
-        <v>1.714630599221783</v>
+        <v>1.990270991807351</v>
       </c>
       <c r="AK2">
-        <v>3.151239709582452</v>
+        <v>3.209285373581833</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>1064.331727353079</v>
+        <v>1307.35391947092</v>
       </c>
       <c r="AP2">
-        <v>-346.6840935291019</v>
+        <v>-398.6241371647774</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mitsubishi UFJ Financial Group, Inc. (TSE:8306)</t>
+          <t>JAPAN POST BANK Co., Ltd. (TSE:7182)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0188</v>
+        <v>0.00127</v>
       </c>
       <c r="E3">
-        <v>0.122</v>
+        <v>0.0107</v>
       </c>
       <c r="F3">
-        <v>0.0751</v>
+        <v>0.083</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,82 +734,82 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.008355877141823096</v>
+        <v>0.0001087520543447559</v>
       </c>
       <c r="J3">
-        <v>0.008355877141823096</v>
+        <v>7.841953146852004e-05</v>
       </c>
       <c r="K3">
-        <v>-4379.5</v>
+        <v>2334</v>
       </c>
       <c r="L3">
-        <v>-0.1761537780852553</v>
+        <v>0.2101547798056924</v>
       </c>
       <c r="M3">
-        <v>4999</v>
+        <v>2217.127</v>
       </c>
       <c r="N3">
-        <v>0.05938112490348637</v>
+        <v>0.06018635799737769</v>
       </c>
       <c r="O3">
-        <v>-1.141454503938806</v>
+        <v>0.9499258783204798</v>
       </c>
       <c r="P3">
-        <v>2307.4</v>
+        <v>1211.427</v>
       </c>
       <c r="Q3">
-        <v>0.02740868325711231</v>
+        <v>0.03288552216886505</v>
       </c>
       <c r="R3">
-        <v>-0.5268637972371275</v>
+        <v>0.51903470437018</v>
       </c>
       <c r="S3">
-        <v>2691.6</v>
+        <v>1005.7</v>
       </c>
       <c r="T3">
-        <v>0.5384276855371074</v>
+        <v>0.4536050483350751</v>
       </c>
       <c r="U3">
-        <v>707587.1</v>
+        <v>423762.8</v>
       </c>
       <c r="V3">
-        <v>8.405144621963533</v>
+        <v>11.50350863381807</v>
       </c>
       <c r="W3">
-        <v>-0.02744413884810441</v>
+        <v>0.03577384309782475</v>
       </c>
       <c r="X3">
-        <v>0.2531494847067445</v>
+        <v>0.1273811387101744</v>
       </c>
       <c r="Y3">
-        <v>-0.2805936235548489</v>
+        <v>-0.09160729561234962</v>
       </c>
       <c r="AB3">
-        <v>0.0728246364000876</v>
+        <v>0.05617625161639223</v>
       </c>
       <c r="AD3">
-        <v>631009.7</v>
+        <v>159062.5</v>
       </c>
       <c r="AE3">
-        <v>2626.289268377113</v>
+        <v>14.41094404620853</v>
       </c>
       <c r="AF3">
-        <v>633635.9892683771</v>
+        <v>159076.9109440462</v>
       </c>
       <c r="AG3">
-        <v>-73951.1107316229</v>
+        <v>-264685.8890559538</v>
       </c>
       <c r="AH3">
-        <v>0.8827214566603804</v>
+        <v>0.8119706344386894</v>
       </c>
       <c r="AI3">
-        <v>0.8370221751392957</v>
+        <v>0.7238226983100183</v>
       </c>
       <c r="AJ3">
-        <v>-7.226100340965499</v>
+        <v>1.16167650992808</v>
       </c>
       <c r="AK3">
-        <v>-1.496226143974573</v>
+        <v>1.297546703415445</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -818,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>860.8590723055934</v>
+        <v>38890.58679706602</v>
       </c>
       <c r="AP3">
-        <v>-100.8882820349562</v>
+        <v>-64715.37629729921</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JAPAN POST BANK Co., Ltd. (TSE:7182)</t>
+          <t>SBI Sumishin Net Bank, Ltd. (TSE:7163)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,11 +840,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.0184</v>
-      </c>
-      <c r="E4">
-        <v>-0.0408</v>
+      <c r="F4">
+        <v>0.132</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,82 +850,85 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.0001489874687723761</v>
+        <v>0.004318981518292137</v>
       </c>
       <c r="J4">
-        <v>0.0001083270855589974</v>
+        <v>0.003001494036794765</v>
       </c>
       <c r="K4">
-        <v>1924.1</v>
+        <v>151.5</v>
       </c>
       <c r="L4">
-        <v>0.1937019922885647</v>
+        <v>0.2364232209737828</v>
       </c>
       <c r="M4">
-        <v>1303.568</v>
+        <v>7.540000000000001</v>
       </c>
       <c r="N4">
-        <v>0.04066114980676434</v>
+        <v>0.004556166535742341</v>
       </c>
       <c r="O4">
-        <v>0.6774949326958059</v>
+        <v>0.04976897689768978</v>
       </c>
       <c r="P4">
-        <v>1296.808</v>
+        <v>7.540000000000001</v>
       </c>
       <c r="Q4">
-        <v>0.04045029055531468</v>
+        <v>0.004556166535742341</v>
       </c>
       <c r="R4">
-        <v>0.6739816017878489</v>
+        <v>0.04976897689768978</v>
       </c>
       <c r="S4">
-        <v>6.759999999999991</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.005185767063935284</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>416112.2</v>
+        <v>7902.9</v>
       </c>
       <c r="V4">
-        <v>12.97945369986244</v>
-      </c>
-      <c r="W4">
-        <v>0.01874329065981916</v>
+        <v>4.775454710254396</v>
       </c>
       <c r="X4">
-        <v>0.173005325020786</v>
-      </c>
-      <c r="Y4">
-        <v>-0.1542620343609668</v>
+        <v>0.1038045899641837</v>
+      </c>
+      <c r="Z4">
+        <v>78.5103305274592</v>
+      </c>
+      <c r="AA4">
+        <v>0.2356482889049548</v>
       </c>
       <c r="AB4">
-        <v>0.07138013236486049</v>
+        <v>0.05866964875246655</v>
+      </c>
+      <c r="AC4">
+        <v>0.1769786401524882</v>
       </c>
       <c r="AD4">
-        <v>135468.3</v>
+        <v>4601.3</v>
       </c>
       <c r="AE4">
-        <v>3.700313882216781</v>
+        <v>8.161983215391997</v>
       </c>
       <c r="AF4">
-        <v>135472.0003138822</v>
+        <v>4609.461983215392</v>
       </c>
       <c r="AG4">
-        <v>-280640.1996861178</v>
+        <v>-3293.438016784607</v>
       </c>
       <c r="AH4">
-        <v>0.8086369535726485</v>
+        <v>0.7358230567719256</v>
       </c>
       <c r="AI4">
-        <v>0.6740286140864608</v>
+        <v>0.8328654162219763</v>
       </c>
       <c r="AJ4">
-        <v>1.128969281390811</v>
+        <v>2.009985720836371</v>
       </c>
       <c r="AK4">
-        <v>1.304552683389109</v>
+        <v>1.390552758165814</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -937,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>61021.75675675675</v>
+        <v>1045.75</v>
       </c>
       <c r="AP4">
-        <v>-126414.5043631161</v>
+        <v>-748.5086401783199</v>
       </c>
     </row>
     <row r="5">
@@ -951,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sumitomo Mitsui Trust Holdings, Inc. (TSE:8309)</t>
+          <t>Rakuten Bank, Ltd. (TSE:5838)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -959,11 +959,8 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.00868</v>
-      </c>
-      <c r="E5">
-        <v>0.0827</v>
+      <c r="F5">
+        <v>0.0663</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,91 +969,82 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.001325548977612136</v>
+        <v>0.004860326937002975</v>
       </c>
       <c r="J5">
-        <v>0.0009796064644394197</v>
+        <v>0.003342417180048582</v>
       </c>
       <c r="K5">
-        <v>1120.2</v>
+        <v>207.4</v>
       </c>
       <c r="L5">
-        <v>0.1447342920268228</v>
+        <v>0.2645408163265306</v>
       </c>
       <c r="M5">
-        <v>679.4930000000001</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.05420030789601729</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.6065818603820746</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>471.9930000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03764890282131662</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.4213470808784146</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>207.5</v>
-      </c>
-      <c r="T5">
-        <v>0.305374742638997</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>136002.9</v>
+        <v>27809.2</v>
       </c>
       <c r="V5">
-        <v>10.84838115293498</v>
-      </c>
-      <c r="W5">
-        <v>0.04519286241633753</v>
+        <v>10.63774768571647</v>
       </c>
       <c r="X5">
-        <v>0.3059520170908939</v>
-      </c>
-      <c r="Y5">
-        <v>-0.2607591546745563</v>
+        <v>0.1526034413589269</v>
       </c>
       <c r="Z5">
-        <v>29.80209224141997</v>
+        <v>34.84828796752366</v>
       </c>
       <c r="AA5">
-        <v>0.02919432221351488</v>
+        <v>0.1164775163979314</v>
       </c>
       <c r="AB5">
-        <v>0.06752875574917733</v>
+        <v>0.0582935132674051</v>
       </c>
       <c r="AC5">
-        <v>-0.03833443353566245</v>
+        <v>0.05818400313052625</v>
       </c>
       <c r="AD5">
-        <v>121512.6</v>
+        <v>15553.7</v>
       </c>
       <c r="AE5">
-        <v>113.2032428898767</v>
+        <v>22.49751840694834</v>
       </c>
       <c r="AF5">
-        <v>121625.8032428899</v>
+        <v>15576.19751840695</v>
       </c>
       <c r="AG5">
-        <v>-14377.09675711011</v>
+        <v>-12233.00248159305</v>
       </c>
       <c r="AH5">
-        <v>0.9065558580305902</v>
+        <v>0.8562868130091891</v>
       </c>
       <c r="AI5">
-        <v>0.8647660574431875</v>
+        <v>0.8995576048340119</v>
       </c>
       <c r="AJ5">
-        <v>7.811955058911227</v>
+        <v>1.271780193532682</v>
       </c>
       <c r="AK5">
-        <v>-3.096508015394263</v>
+        <v>1.165735919181888</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1065,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>3693.392097264438</v>
+        <v>1871.684717208183</v>
       </c>
       <c r="AP5">
-        <v>-436.9938224045625</v>
+        <v>-1472.082127748863</v>
       </c>
     </row>
     <row r="6">
@@ -1079,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aozora Bank, Ltd. (TSE:8304)</t>
+          <t>Mitsubishi UFJ Financial Group, Inc. (TSE:8306)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,13 +1076,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.007209999999999999</v>
+        <v>-0.018</v>
       </c>
       <c r="E6">
-        <v>-0.0555</v>
+        <v>0.006939999999999999</v>
       </c>
       <c r="F6">
-        <v>0.0143</v>
+        <v>0.142</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1103,91 +1091,91 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.00941093275580126</v>
+        <v>0.007642005582307715</v>
       </c>
       <c r="J6">
-        <v>0.006764320258772675</v>
+        <v>0.007414323162531733</v>
       </c>
       <c r="K6">
-        <v>213.9</v>
+        <v>8677.6</v>
       </c>
       <c r="L6">
-        <v>0.2569369369369369</v>
+        <v>0.3183353937922104</v>
       </c>
       <c r="M6">
-        <v>129.648</v>
+        <v>3958</v>
       </c>
       <c r="N6">
-        <v>0.0564177545691906</v>
+        <v>0.03844136671781823</v>
       </c>
       <c r="O6">
-        <v>0.6061150070126227</v>
+        <v>0.4561168986816631</v>
       </c>
       <c r="P6">
-        <v>129.648</v>
+        <v>2540.7</v>
       </c>
       <c r="Q6">
-        <v>0.0564177545691906</v>
+        <v>0.02467609409296634</v>
       </c>
       <c r="R6">
-        <v>0.6061150070126227</v>
+        <v>0.2927883285701115</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1417.3</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.3580848913592724</v>
       </c>
       <c r="U6">
-        <v>6711.5</v>
+        <v>727262.8</v>
       </c>
       <c r="V6">
-        <v>2.920583115752828</v>
+        <v>7.063409801674404</v>
       </c>
       <c r="W6">
-        <v>0.0457510747973392</v>
+        <v>0.07463960089454671</v>
       </c>
       <c r="X6">
-        <v>0.1422752058348026</v>
+        <v>0.1557453599150105</v>
       </c>
       <c r="Y6">
-        <v>-0.09652413103746341</v>
+        <v>-0.08110575902046382</v>
       </c>
       <c r="Z6">
-        <v>0.1820855391674471</v>
+        <v>0.6513724597875752</v>
       </c>
       <c r="AA6">
-        <v>0.001231684901419908</v>
+        <v>0.004829485916038289</v>
       </c>
       <c r="AB6">
-        <v>0.07354576888970157</v>
+        <v>0.05668749331717567</v>
       </c>
       <c r="AC6">
-        <v>-0.07231408398828167</v>
+        <v>-0.05185800740113738</v>
       </c>
       <c r="AD6">
-        <v>6754.1</v>
+        <v>632346.7</v>
       </c>
       <c r="AE6">
-        <v>47.82699240397725</v>
+        <v>2166.421386150997</v>
       </c>
       <c r="AF6">
-        <v>6801.926992403977</v>
+        <v>634513.1213861509</v>
       </c>
       <c r="AG6">
-        <v>90.42699240397724</v>
+        <v>-92749.6786138491</v>
       </c>
       <c r="AH6">
-        <v>0.7474705014756471</v>
+        <v>0.8603857987690844</v>
       </c>
       <c r="AI6">
-        <v>0.6916866645770812</v>
+        <v>0.8285136298024671</v>
       </c>
       <c r="AJ6">
-        <v>0.03786048001113967</v>
+        <v>-9.082134718128682</v>
       </c>
       <c r="AK6">
-        <v>0.02896141007138867</v>
+        <v>-2.40394240889667</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1196,10 +1184,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>388.1666666666667</v>
+        <v>985.5777743142144</v>
       </c>
       <c r="AP6">
-        <v>5.196953586435474</v>
+        <v>-144.5599729018845</v>
       </c>
     </row>
     <row r="7">
@@ -1210,127 +1198,389 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Sumitomo Mitsui Trust Holdings, Inc. (TSE:8309)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.00482</v>
+      </c>
+      <c r="E7">
+        <v>-0.0508</v>
+      </c>
+      <c r="F7">
+        <v>0.128</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0.0007500499395392238</v>
+      </c>
+      <c r="J7">
+        <v>0.0005451654735798505</v>
+      </c>
+      <c r="K7">
+        <v>877.3</v>
+      </c>
+      <c r="L7">
+        <v>0.1208219140350636</v>
+      </c>
+      <c r="M7">
+        <v>677.9567999999999</v>
+      </c>
+      <c r="N7">
+        <v>0.04862694018074881</v>
+      </c>
+      <c r="O7">
+        <v>0.772776473270261</v>
+      </c>
+      <c r="P7">
+        <v>534.5568</v>
+      </c>
+      <c r="Q7">
+        <v>0.03834147181179171</v>
+      </c>
+      <c r="R7">
+        <v>0.609320414909381</v>
+      </c>
+      <c r="S7">
+        <v>143.4</v>
+      </c>
+      <c r="T7">
+        <v>0.2115179020256158</v>
+      </c>
+      <c r="U7">
+        <v>149014.1</v>
+      </c>
+      <c r="V7">
+        <v>10.68814373834457</v>
+      </c>
+      <c r="W7">
+        <v>0.04661728447542934</v>
+      </c>
+      <c r="X7">
+        <v>0.1987686819324703</v>
+      </c>
+      <c r="Y7">
+        <v>-0.152151397457041</v>
+      </c>
+      <c r="Z7">
+        <v>1.639381992082337</v>
+      </c>
+      <c r="AA7">
+        <v>0.0008937344600918461</v>
+      </c>
+      <c r="AB7">
+        <v>0.05286493219150611</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05197119773141427</v>
+      </c>
+      <c r="AD7">
+        <v>124820.4</v>
+      </c>
+      <c r="AE7">
+        <v>100.2690619200587</v>
+      </c>
+      <c r="AF7">
+        <v>124920.6690619201</v>
+      </c>
+      <c r="AG7">
+        <v>-24093.43093807995</v>
+      </c>
+      <c r="AH7">
+        <v>0.8995986459558606</v>
+      </c>
+      <c r="AI7">
+        <v>0.862483262349599</v>
+      </c>
+      <c r="AJ7">
+        <v>2.373402438044562</v>
+      </c>
+      <c r="AK7">
+        <v>5.769871501624666</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>4894.917647058824</v>
+      </c>
+      <c r="AP7">
+        <v>-944.8404289443118</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Aozora Bank, Ltd. (TSE:8304)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.0291</v>
+      </c>
+      <c r="E8">
+        <v>-0.335</v>
+      </c>
+      <c r="F8">
+        <v>0.508</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.01344206540666206</v>
+      </c>
+      <c r="J8">
+        <v>0.01344206540666206</v>
+      </c>
+      <c r="K8">
+        <v>36</v>
+      </c>
+      <c r="L8">
+        <v>0.0525164113785558</v>
+      </c>
+      <c r="M8">
+        <v>120.304</v>
+      </c>
+      <c r="N8">
+        <v>0.04739363378506146</v>
+      </c>
+      <c r="O8">
+        <v>3.341777777777778</v>
+      </c>
+      <c r="P8">
+        <v>120.304</v>
+      </c>
+      <c r="Q8">
+        <v>0.04739363378506146</v>
+      </c>
+      <c r="R8">
+        <v>3.341777777777778</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>9423.1</v>
+      </c>
+      <c r="V8">
+        <v>3.712220296249606</v>
+      </c>
+      <c r="W8">
+        <v>0.01168148484651827</v>
+      </c>
+      <c r="X8">
+        <v>0.1082069909185518</v>
+      </c>
+      <c r="Y8">
+        <v>-0.09652550607203358</v>
+      </c>
+      <c r="Z8">
+        <v>0.2167707294204247</v>
+      </c>
+      <c r="AA8">
+        <v>0.002913846323119193</v>
+      </c>
+      <c r="AB8">
+        <v>0.05861165736432473</v>
+      </c>
+      <c r="AC8">
+        <v>-0.05569781104120553</v>
+      </c>
+      <c r="AD8">
+        <v>7759</v>
+      </c>
+      <c r="AE8">
+        <v>37.92732081866579</v>
+      </c>
+      <c r="AF8">
+        <v>7796.927320818666</v>
+      </c>
+      <c r="AG8">
+        <v>-1626.172679181334</v>
+      </c>
+      <c r="AH8">
+        <v>0.7543957804909722</v>
+      </c>
+      <c r="AI8">
+        <v>0.7280977372011671</v>
+      </c>
+      <c r="AJ8">
+        <v>-1.7826397456743</v>
+      </c>
+      <c r="AK8">
+        <v>-1.26498492318758</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>461.8452380952381</v>
+      </c>
+      <c r="AP8">
+        <v>-96.79599280841276</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Mizuho Financial Group, Inc. (TSE:8411)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.0147</v>
-      </c>
-      <c r="E7">
-        <v>-0.0315</v>
-      </c>
-      <c r="F7">
-        <v>0.0616</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0.001376749498371223</v>
-      </c>
-      <c r="J7">
-        <v>0.001117691200573064</v>
-      </c>
-      <c r="K7">
-        <v>3309.1</v>
-      </c>
-      <c r="L7">
-        <v>0.1891984608435629</v>
-      </c>
-      <c r="M7">
-        <v>1413.38</v>
-      </c>
-      <c r="N7">
-        <v>0.03962588419343896</v>
-      </c>
-      <c r="O7">
-        <v>0.4271191562660542</v>
-      </c>
-      <c r="P7">
-        <v>1403.9</v>
-      </c>
-      <c r="Q7">
-        <v>0.03936010048194325</v>
-      </c>
-      <c r="R7">
-        <v>0.4242543289716237</v>
-      </c>
-      <c r="S7">
-        <v>9.480000000000018</v>
-      </c>
-      <c r="T7">
-        <v>0.006707325701509869</v>
-      </c>
-      <c r="U7">
-        <v>366439.9</v>
-      </c>
-      <c r="V7">
-        <v>10.2736030234299</v>
-      </c>
-      <c r="W7">
-        <v>0.03875577688403133</v>
-      </c>
-      <c r="X7">
-        <v>0.2986010864311068</v>
-      </c>
-      <c r="Y7">
-        <v>-0.2598453095470755</v>
-      </c>
-      <c r="Z7">
-        <v>0.1786304417761866</v>
-      </c>
-      <c r="AA7">
-        <v>0.0001996536729277227</v>
-      </c>
-      <c r="AB7">
-        <v>0.07288232993623946</v>
-      </c>
-      <c r="AC7">
-        <v>-0.07268267626331174</v>
-      </c>
-      <c r="AD7">
-        <v>333515.4</v>
-      </c>
-      <c r="AE7">
-        <v>1722.102567992687</v>
-      </c>
-      <c r="AF7">
-        <v>335237.5025679927</v>
-      </c>
-      <c r="AG7">
-        <v>-31202.3974320073</v>
-      </c>
-      <c r="AH7">
-        <v>0.9038351004863523</v>
-      </c>
-      <c r="AI7">
-        <v>0.8435483454934639</v>
-      </c>
-      <c r="AJ7">
-        <v>-6.987119486113151</v>
-      </c>
-      <c r="AK7">
-        <v>-1.007386769540688</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>905.062143826323</v>
-      </c>
-      <c r="AP7">
-        <v>-84.67407715605781</v>
+      <c r="D9">
+        <v>0.00766</v>
+      </c>
+      <c r="E9">
+        <v>0.005759999999999999</v>
+      </c>
+      <c r="F9">
+        <v>0.124</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0.0006325871240211485</v>
+      </c>
+      <c r="J9">
+        <v>0.0004352540693409482</v>
+      </c>
+      <c r="K9">
+        <v>4266.9</v>
+      </c>
+      <c r="L9">
+        <v>0.2215133030499675</v>
+      </c>
+      <c r="M9">
+        <v>1569.0412</v>
+      </c>
+      <c r="N9">
+        <v>0.03616827371910276</v>
+      </c>
+      <c r="O9">
+        <v>0.3677239213480513</v>
+      </c>
+      <c r="P9">
+        <v>1569.0412</v>
+      </c>
+      <c r="Q9">
+        <v>0.03616827371910276</v>
+      </c>
+      <c r="R9">
+        <v>0.3677239213480513</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>412838</v>
+      </c>
+      <c r="V9">
+        <v>9.516408992731959</v>
+      </c>
+      <c r="W9">
+        <v>0.06918586739740243</v>
+      </c>
+      <c r="X9">
+        <v>0.2033608074805924</v>
+      </c>
+      <c r="Y9">
+        <v>-0.13417494008319</v>
+      </c>
+      <c r="Z9">
+        <v>0.6352004295223567</v>
+      </c>
+      <c r="AA9">
+        <v>0.0002764735717967239</v>
+      </c>
+      <c r="AB9">
+        <v>0.05647790703276944</v>
+      </c>
+      <c r="AC9">
+        <v>-0.05620143346097271</v>
+      </c>
+      <c r="AD9">
+        <v>400077.7</v>
+      </c>
+      <c r="AE9">
+        <v>1576.573952617713</v>
+      </c>
+      <c r="AF9">
+        <v>401654.2739526177</v>
+      </c>
+      <c r="AG9">
+        <v>-11183.72604738228</v>
+      </c>
+      <c r="AH9">
+        <v>0.902520913950613</v>
+      </c>
+      <c r="AI9">
+        <v>0.8613917195966013</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.3473425397461395</v>
+      </c>
+      <c r="AK9">
+        <v>-0.2092478291277666</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>1221.611297709924</v>
+      </c>
+      <c r="AP9">
+        <v>-34.14878182406804</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/japan/japan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00127</v>
+        <v>0.0837</v>
       </c>
       <c r="E2">
-        <v>0.005759999999999999</v>
+        <v>0.194</v>
       </c>
       <c r="F2">
-        <v>0.128</v>
+        <v>0.127</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.0036261209679027</v>
+        <v>0.00170213587187489</v>
       </c>
       <c r="J2">
-        <v>0.002843310271242587</v>
+        <v>0.001348003674375868</v>
       </c>
       <c r="K2">
-        <v>16550.7</v>
+        <v>24599.4</v>
       </c>
       <c r="L2">
-        <v>0.2470279540234002</v>
+        <v>0.2580403559785003</v>
       </c>
       <c r="M2">
-        <v>8549.968999999999</v>
+        <v>12964.876</v>
       </c>
       <c r="N2">
-        <v>0.04192581408702653</v>
+        <v>0.04399965247917421</v>
       </c>
       <c r="O2">
-        <v>0.5165925912499169</v>
+        <v>0.5270403343170972</v>
       </c>
       <c r="P2">
-        <v>5983.569</v>
+        <v>7549.776000000001</v>
       </c>
       <c r="Q2">
-        <v>0.02934115918676375</v>
+        <v>0.02562211318454646</v>
       </c>
       <c r="R2">
-        <v>0.3615296633979227</v>
+        <v>0.3069089489987561</v>
       </c>
       <c r="S2">
-        <v>2566.4</v>
+        <v>5415.1</v>
       </c>
       <c r="T2">
-        <v>0.3001648310069897</v>
+        <v>0.4176746464833139</v>
       </c>
       <c r="U2">
-        <v>1758012.9</v>
+        <v>1725223.1</v>
       </c>
       <c r="V2">
-        <v>8.620630321349045</v>
+        <v>5.854989808544533</v>
       </c>
       <c r="W2">
-        <v>0.06918586739740243</v>
+        <v>0.08302886704418203</v>
       </c>
       <c r="X2">
-        <v>0.1526034413589269</v>
+        <v>0.1316342146376442</v>
       </c>
       <c r="Y2">
-        <v>-0.08341757396152447</v>
+        <v>-0.04860534759346216</v>
       </c>
       <c r="Z2">
-        <v>0.8396296689759727</v>
+        <v>0.6964216354199241</v>
       </c>
       <c r="AA2">
-        <v>0.004829485916038289</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05668749331717567</v>
+        <v>0.05923924539036013</v>
       </c>
       <c r="AC2">
-        <v>-0.05185800740113738</v>
+        <v>-0.05898390013570374</v>
       </c>
       <c r="AD2">
-        <v>1344221.3</v>
+        <v>1521441.9</v>
       </c>
       <c r="AE2">
-        <v>3926.262167175983</v>
+        <v>1844.163319583859</v>
       </c>
       <c r="AF2">
-        <v>1348147.562167176</v>
+        <v>1523286.063319584</v>
       </c>
       <c r="AG2">
-        <v>-409865.3378328241</v>
+        <v>-201937.0366804162</v>
       </c>
       <c r="AH2">
-        <v>0.8686078668244323</v>
+        <v>0.8379166286272154</v>
       </c>
       <c r="AI2">
-        <v>0.8269319127112789</v>
+        <v>0.8203435497510495</v>
       </c>
       <c r="AJ2">
-        <v>1.990270991807351</v>
+        <v>-2.177886453277314</v>
       </c>
       <c r="AK2">
-        <v>3.209285373581833</v>
+        <v>-1.533720019062824</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>1307.35391947092</v>
+        <v>2864.699491621163</v>
       </c>
       <c r="AP2">
-        <v>-398.6241371647774</v>
+        <v>-380.2241323299119</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JAPAN POST BANK Co., Ltd. (TSE:7182)</t>
+          <t>Mitsubishi UFJ Financial Group, Inc. (TSE:8306)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00127</v>
+        <v>0.08839999999999999</v>
       </c>
       <c r="E3">
-        <v>0.0107</v>
+        <v>0.194</v>
       </c>
       <c r="F3">
-        <v>0.083</v>
+        <v>0.114</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,82 +734,91 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.0001087520543447559</v>
+        <v>0.003968571200012429</v>
       </c>
       <c r="J3">
-        <v>7.841953146852004e-05</v>
+        <v>0.002878333436178002</v>
       </c>
       <c r="K3">
-        <v>2334</v>
+        <v>11580.3</v>
       </c>
       <c r="L3">
-        <v>0.2101547798056924</v>
+        <v>0.2832193229815032</v>
       </c>
       <c r="M3">
-        <v>2217.127</v>
+        <v>6681.6</v>
       </c>
       <c r="N3">
-        <v>0.06018635799737769</v>
+        <v>0.04887297240362334</v>
       </c>
       <c r="O3">
-        <v>0.9499258783204798</v>
+        <v>0.5769798709877983</v>
       </c>
       <c r="P3">
-        <v>1211.427</v>
+        <v>3062.3</v>
       </c>
       <c r="Q3">
-        <v>0.03288552216886505</v>
+        <v>0.02239938089553636</v>
       </c>
       <c r="R3">
-        <v>0.51903470437018</v>
+        <v>0.2644404721812043</v>
       </c>
       <c r="S3">
-        <v>1005.7</v>
+        <v>3619.3</v>
       </c>
       <c r="T3">
-        <v>0.4536050483350751</v>
+        <v>0.5416816331417624</v>
       </c>
       <c r="U3">
-        <v>423762.8</v>
+        <v>753869.9</v>
       </c>
       <c r="V3">
-        <v>11.50350863381807</v>
+        <v>5.514227553074456</v>
       </c>
       <c r="W3">
-        <v>0.03577384309782475</v>
+        <v>0.09338793455917278</v>
       </c>
       <c r="X3">
-        <v>0.1273811387101744</v>
+        <v>0.1345323738216071</v>
       </c>
       <c r="Y3">
-        <v>-0.09160729561234962</v>
+        <v>-0.04114443926243434</v>
+      </c>
+      <c r="Z3">
+        <v>1.32194904946109</v>
+      </c>
+      <c r="AA3">
+        <v>0.003805010149987582</v>
       </c>
       <c r="AB3">
-        <v>0.05617625161639223</v>
+        <v>0.05918006114963659</v>
+      </c>
+      <c r="AC3">
+        <v>-0.055375050999649</v>
       </c>
       <c r="AD3">
-        <v>159062.5</v>
+        <v>643332</v>
       </c>
       <c r="AE3">
-        <v>14.41094404620853</v>
+        <v>1844.163319583859</v>
       </c>
       <c r="AF3">
-        <v>159076.9109440462</v>
+        <v>645176.1633195839</v>
       </c>
       <c r="AG3">
-        <v>-264685.8890559538</v>
+        <v>-108693.7366804162</v>
       </c>
       <c r="AH3">
-        <v>0.8119706344386894</v>
+        <v>0.8251497763321903</v>
       </c>
       <c r="AI3">
-        <v>0.7238226983100183</v>
+        <v>0.8100188325422784</v>
       </c>
       <c r="AJ3">
-        <v>1.16167650992808</v>
+        <v>-3.879167269329509</v>
       </c>
       <c r="AK3">
-        <v>1.297546703415445</v>
+        <v>-2.549977952457188</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -818,10 +827,10 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>38890.58679706602</v>
+        <v>1211.319902090002</v>
       </c>
       <c r="AP3">
-        <v>-64715.37629729921</v>
+        <v>-204.6577606484959</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SBI Sumishin Net Bank, Ltd. (TSE:7163)</t>
+          <t>Mizuho Financial Group, Inc. (TSE:8411)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,8 +849,14 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.079</v>
+      </c>
+      <c r="E4">
+        <v>1.017</v>
+      </c>
       <c r="F4">
-        <v>0.132</v>
+        <v>0.138</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -850,97 +865,97 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.004318981518292137</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0.003001494036794765</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>151.5</v>
+        <v>5789.2</v>
       </c>
       <c r="L4">
-        <v>0.2364232209737828</v>
+        <v>0.2314309928522315</v>
       </c>
       <c r="M4">
-        <v>7.540000000000001</v>
+        <v>1886.4</v>
       </c>
       <c r="N4">
-        <v>0.004556166535742341</v>
+        <v>0.03027900212839042</v>
       </c>
       <c r="O4">
-        <v>0.04976897689768978</v>
+        <v>0.3258481310025565</v>
       </c>
       <c r="P4">
-        <v>7.540000000000001</v>
+        <v>1859.9</v>
       </c>
       <c r="Q4">
-        <v>0.004556166535742341</v>
+        <v>0.02985364506922887</v>
       </c>
       <c r="R4">
-        <v>0.04976897689768978</v>
+        <v>0.3212706418848891</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.01404792196776929</v>
       </c>
       <c r="U4">
-        <v>7902.9</v>
+        <v>487747.8</v>
       </c>
       <c r="V4">
-        <v>4.775454710254396</v>
+        <v>7.828942257377938</v>
+      </c>
+      <c r="W4">
+        <v>0.09028991903976892</v>
       </c>
       <c r="X4">
-        <v>0.1038045899641837</v>
+        <v>0.1744773465414663</v>
+      </c>
+      <c r="Y4">
+        <v>-0.08418742750169735</v>
       </c>
       <c r="Z4">
-        <v>78.5103305274592</v>
+        <v>0.487071046933657</v>
       </c>
       <c r="AA4">
-        <v>0.2356482889049548</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05866964875246655</v>
+        <v>0.05866937064032381</v>
       </c>
       <c r="AC4">
-        <v>0.1769786401524882</v>
+        <v>-0.05866937064032381</v>
       </c>
       <c r="AD4">
-        <v>4601.3</v>
+        <v>466786.2</v>
       </c>
       <c r="AE4">
-        <v>8.161983215391997</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>4609.461983215392</v>
+        <v>466786.2</v>
       </c>
       <c r="AG4">
-        <v>-3293.438016784607</v>
+        <v>-20961.59999999998</v>
       </c>
       <c r="AH4">
-        <v>0.7358230567719256</v>
+        <v>0.8822488105921372</v>
       </c>
       <c r="AI4">
-        <v>0.8328654162219763</v>
+        <v>0.8613856946326962</v>
       </c>
       <c r="AJ4">
-        <v>2.009985720836371</v>
+        <v>-0.5070659667626204</v>
       </c>
       <c r="AK4">
-        <v>1.390552758165814</v>
+        <v>-0.3870760446654609</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
         <v>0</v>
-      </c>
-      <c r="AN4">
-        <v>1045.75</v>
-      </c>
-      <c r="AP4">
-        <v>-748.5086401783199</v>
       </c>
     </row>
     <row r="5">
@@ -951,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rakuten Bank, Ltd. (TSE:5838)</t>
+          <t>Sumitomo Mitsui Financial Group, Inc. (TSE:8316)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -959,8 +974,14 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.138</v>
+      </c>
+      <c r="E5">
+        <v>0.162</v>
+      </c>
       <c r="F5">
-        <v>0.0663</v>
+        <v>0.116</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -969,94 +990,97 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.004860326937002975</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0.003342417180048582</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>207.4</v>
+        <v>7579.1</v>
       </c>
       <c r="L5">
-        <v>0.2645408163265306</v>
+        <v>0.2611249689920344</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>4360.2</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.0466541619274561</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.575292580913301</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>2590.9</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.02772264302964223</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.341847976672692</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1769.3</v>
+      </c>
+      <c r="T5">
+        <v>0.4057841383422778</v>
       </c>
       <c r="U5">
-        <v>27809.2</v>
+        <v>471255.4</v>
       </c>
       <c r="V5">
-        <v>10.63774768571647</v>
+        <v>5.042435149944521</v>
+      </c>
+      <c r="W5">
+        <v>0.07576781504859513</v>
       </c>
       <c r="X5">
-        <v>0.1526034413589269</v>
+        <v>0.1287360554536813</v>
+      </c>
+      <c r="Y5">
+        <v>-0.05296824040508614</v>
       </c>
       <c r="Z5">
-        <v>34.84828796752366</v>
+        <v>0.5435131885952269</v>
       </c>
       <c r="AA5">
-        <v>0.1164775163979314</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0582935132674051</v>
+        <v>0.05929842963108367</v>
       </c>
       <c r="AC5">
-        <v>0.05818400313052625</v>
+        <v>-0.05929842963108367</v>
       </c>
       <c r="AD5">
-        <v>15553.7</v>
+        <v>403434.7</v>
       </c>
       <c r="AE5">
-        <v>22.49751840694834</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>15576.19751840695</v>
+        <v>403434.7</v>
       </c>
       <c r="AG5">
-        <v>-12233.00248159305</v>
+        <v>-67820.70000000001</v>
       </c>
       <c r="AH5">
-        <v>0.8562868130091891</v>
+        <v>0.8119152911514481</v>
       </c>
       <c r="AI5">
-        <v>0.8995576048340119</v>
+        <v>0.7951210100045764</v>
       </c>
       <c r="AJ5">
-        <v>1.271780193532682</v>
+        <v>-2.645401993977504</v>
       </c>
       <c r="AK5">
-        <v>1.165735919181888</v>
+        <v>-1.877005125593651</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>1871.684717208183</v>
-      </c>
-      <c r="AP5">
-        <v>-1472.082127748863</v>
       </c>
     </row>
     <row r="6">
@@ -1067,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mitsubishi UFJ Financial Group, Inc. (TSE:8306)</t>
+          <t>Aozora Bank, Ltd. (TSE:8304)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,13 +1100,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.018</v>
-      </c>
-      <c r="E6">
-        <v>0.006939999999999999</v>
+        <v>-0.123</v>
       </c>
       <c r="F6">
-        <v>0.142</v>
+        <v>0.398</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1091,496 +1112,97 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.007642005582307715</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.007414323162531733</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>8677.6</v>
+        <v>-349.2</v>
       </c>
       <c r="L6">
-        <v>0.3183353937922104</v>
+        <v>-0.864570438227284</v>
       </c>
       <c r="M6">
-        <v>3958</v>
+        <v>36.676</v>
       </c>
       <c r="N6">
-        <v>0.03844136671781823</v>
+        <v>0.01677383946947176</v>
       </c>
       <c r="O6">
-        <v>0.4561168986816631</v>
+        <v>-0.105028636884307</v>
       </c>
       <c r="P6">
-        <v>2540.7</v>
+        <v>36.676</v>
       </c>
       <c r="Q6">
-        <v>0.02467609409296634</v>
+        <v>0.01677383946947176</v>
       </c>
       <c r="R6">
-        <v>0.2927883285701115</v>
+        <v>-0.105028636884307</v>
       </c>
       <c r="S6">
-        <v>1417.3</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.3580848913592724</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>727262.8</v>
+        <v>12350</v>
       </c>
       <c r="V6">
-        <v>7.063409801674404</v>
+        <v>5.648296364052138</v>
       </c>
       <c r="W6">
-        <v>0.07463960089454671</v>
+        <v>-0.1220168419581397</v>
       </c>
       <c r="X6">
-        <v>0.1557453599150105</v>
+        <v>0.1185283131244147</v>
       </c>
       <c r="Y6">
-        <v>-0.08110575902046382</v>
+        <v>-0.2405451550825544</v>
       </c>
       <c r="Z6">
-        <v>0.6513724597875752</v>
+        <v>0.3372015361496078</v>
       </c>
       <c r="AA6">
-        <v>0.004829485916038289</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05668749331717567</v>
+        <v>0.06091524320838732</v>
       </c>
       <c r="AC6">
-        <v>-0.05185800740113738</v>
+        <v>-0.06091524320838732</v>
       </c>
       <c r="AD6">
-        <v>632346.7</v>
+        <v>7889</v>
       </c>
       <c r="AE6">
-        <v>2166.421386150997</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>634513.1213861509</v>
+        <v>7889</v>
       </c>
       <c r="AG6">
-        <v>-92749.6786138491</v>
+        <v>-4461</v>
       </c>
       <c r="AH6">
-        <v>0.8603857987690844</v>
+        <v>0.7829884372983971</v>
       </c>
       <c r="AI6">
-        <v>0.8285136298024671</v>
+        <v>0.7105030891438658</v>
       </c>
       <c r="AJ6">
-        <v>-9.082134718128682</v>
+        <v>1.961310178061112</v>
       </c>
       <c r="AK6">
-        <v>-2.40394240889667</v>
+        <v>3.578533611423071</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>985.5777743142144</v>
-      </c>
-      <c r="AP6">
-        <v>-144.5599729018845</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Sumitomo Mitsui Trust Holdings, Inc. (TSE:8309)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.00482</v>
-      </c>
-      <c r="E7">
-        <v>-0.0508</v>
-      </c>
-      <c r="F7">
-        <v>0.128</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0.0007500499395392238</v>
-      </c>
-      <c r="J7">
-        <v>0.0005451654735798505</v>
-      </c>
-      <c r="K7">
-        <v>877.3</v>
-      </c>
-      <c r="L7">
-        <v>0.1208219140350636</v>
-      </c>
-      <c r="M7">
-        <v>677.9567999999999</v>
-      </c>
-      <c r="N7">
-        <v>0.04862694018074881</v>
-      </c>
-      <c r="O7">
-        <v>0.772776473270261</v>
-      </c>
-      <c r="P7">
-        <v>534.5568</v>
-      </c>
-      <c r="Q7">
-        <v>0.03834147181179171</v>
-      </c>
-      <c r="R7">
-        <v>0.609320414909381</v>
-      </c>
-      <c r="S7">
-        <v>143.4</v>
-      </c>
-      <c r="T7">
-        <v>0.2115179020256158</v>
-      </c>
-      <c r="U7">
-        <v>149014.1</v>
-      </c>
-      <c r="V7">
-        <v>10.68814373834457</v>
-      </c>
-      <c r="W7">
-        <v>0.04661728447542934</v>
-      </c>
-      <c r="X7">
-        <v>0.1987686819324703</v>
-      </c>
-      <c r="Y7">
-        <v>-0.152151397457041</v>
-      </c>
-      <c r="Z7">
-        <v>1.639381992082337</v>
-      </c>
-      <c r="AA7">
-        <v>0.0008937344600918461</v>
-      </c>
-      <c r="AB7">
-        <v>0.05286493219150611</v>
-      </c>
-      <c r="AC7">
-        <v>-0.05197119773141427</v>
-      </c>
-      <c r="AD7">
-        <v>124820.4</v>
-      </c>
-      <c r="AE7">
-        <v>100.2690619200587</v>
-      </c>
-      <c r="AF7">
-        <v>124920.6690619201</v>
-      </c>
-      <c r="AG7">
-        <v>-24093.43093807995</v>
-      </c>
-      <c r="AH7">
-        <v>0.8995986459558606</v>
-      </c>
-      <c r="AI7">
-        <v>0.862483262349599</v>
-      </c>
-      <c r="AJ7">
-        <v>2.373402438044562</v>
-      </c>
-      <c r="AK7">
-        <v>5.769871501624666</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>4894.917647058824</v>
-      </c>
-      <c r="AP7">
-        <v>-944.8404289443118</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Aozora Bank, Ltd. (TSE:8304)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>-0.0291</v>
-      </c>
-      <c r="E8">
-        <v>-0.335</v>
-      </c>
-      <c r="F8">
-        <v>0.508</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.01344206540666206</v>
-      </c>
-      <c r="J8">
-        <v>0.01344206540666206</v>
-      </c>
-      <c r="K8">
-        <v>36</v>
-      </c>
-      <c r="L8">
-        <v>0.0525164113785558</v>
-      </c>
-      <c r="M8">
-        <v>120.304</v>
-      </c>
-      <c r="N8">
-        <v>0.04739363378506146</v>
-      </c>
-      <c r="O8">
-        <v>3.341777777777778</v>
-      </c>
-      <c r="P8">
-        <v>120.304</v>
-      </c>
-      <c r="Q8">
-        <v>0.04739363378506146</v>
-      </c>
-      <c r="R8">
-        <v>3.341777777777778</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>9423.1</v>
-      </c>
-      <c r="V8">
-        <v>3.712220296249606</v>
-      </c>
-      <c r="W8">
-        <v>0.01168148484651827</v>
-      </c>
-      <c r="X8">
-        <v>0.1082069909185518</v>
-      </c>
-      <c r="Y8">
-        <v>-0.09652550607203358</v>
-      </c>
-      <c r="Z8">
-        <v>0.2167707294204247</v>
-      </c>
-      <c r="AA8">
-        <v>0.002913846323119193</v>
-      </c>
-      <c r="AB8">
-        <v>0.05861165736432473</v>
-      </c>
-      <c r="AC8">
-        <v>-0.05569781104120553</v>
-      </c>
-      <c r="AD8">
-        <v>7759</v>
-      </c>
-      <c r="AE8">
-        <v>37.92732081866579</v>
-      </c>
-      <c r="AF8">
-        <v>7796.927320818666</v>
-      </c>
-      <c r="AG8">
-        <v>-1626.172679181334</v>
-      </c>
-      <c r="AH8">
-        <v>0.7543957804909722</v>
-      </c>
-      <c r="AI8">
-        <v>0.7280977372011671</v>
-      </c>
-      <c r="AJ8">
-        <v>-1.7826397456743</v>
-      </c>
-      <c r="AK8">
-        <v>-1.26498492318758</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>461.8452380952381</v>
-      </c>
-      <c r="AP8">
-        <v>-96.79599280841276</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mizuho Financial Group, Inc. (TSE:8411)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.00766</v>
-      </c>
-      <c r="E9">
-        <v>0.005759999999999999</v>
-      </c>
-      <c r="F9">
-        <v>0.124</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0.0006325871240211485</v>
-      </c>
-      <c r="J9">
-        <v>0.0004352540693409482</v>
-      </c>
-      <c r="K9">
-        <v>4266.9</v>
-      </c>
-      <c r="L9">
-        <v>0.2215133030499675</v>
-      </c>
-      <c r="M9">
-        <v>1569.0412</v>
-      </c>
-      <c r="N9">
-        <v>0.03616827371910276</v>
-      </c>
-      <c r="O9">
-        <v>0.3677239213480513</v>
-      </c>
-      <c r="P9">
-        <v>1569.0412</v>
-      </c>
-      <c r="Q9">
-        <v>0.03616827371910276</v>
-      </c>
-      <c r="R9">
-        <v>0.3677239213480513</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>412838</v>
-      </c>
-      <c r="V9">
-        <v>9.516408992731959</v>
-      </c>
-      <c r="W9">
-        <v>0.06918586739740243</v>
-      </c>
-      <c r="X9">
-        <v>0.2033608074805924</v>
-      </c>
-      <c r="Y9">
-        <v>-0.13417494008319</v>
-      </c>
-      <c r="Z9">
-        <v>0.6352004295223567</v>
-      </c>
-      <c r="AA9">
-        <v>0.0002764735717967239</v>
-      </c>
-      <c r="AB9">
-        <v>0.05647790703276944</v>
-      </c>
-      <c r="AC9">
-        <v>-0.05620143346097271</v>
-      </c>
-      <c r="AD9">
-        <v>400077.7</v>
-      </c>
-      <c r="AE9">
-        <v>1576.573952617713</v>
-      </c>
-      <c r="AF9">
-        <v>401654.2739526177</v>
-      </c>
-      <c r="AG9">
-        <v>-11183.72604738228</v>
-      </c>
-      <c r="AH9">
-        <v>0.902520913950613</v>
-      </c>
-      <c r="AI9">
-        <v>0.8613917195966013</v>
-      </c>
-      <c r="AJ9">
-        <v>-0.3473425397461395</v>
-      </c>
-      <c r="AK9">
-        <v>-0.2092478291277666</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>1221.611297709924</v>
-      </c>
-      <c r="AP9">
-        <v>-34.14878182406804</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/japan/japan_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_bank_money_center.xlsx
@@ -648,10 +648,10 @@
         <v>0.08302886704418203</v>
       </c>
       <c r="X2">
-        <v>0.1316342146376442</v>
+        <v>0.1315963181636294</v>
       </c>
       <c r="Y2">
-        <v>-0.04860534759346216</v>
+        <v>-0.04856745111944735</v>
       </c>
       <c r="Z2">
         <v>0.6964216354199241</v>
@@ -660,10 +660,10 @@
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05923924539036013</v>
+        <v>0.05923237688039844</v>
       </c>
       <c r="AC2">
-        <v>-0.05898390013570374</v>
+        <v>-0.05897711175163547</v>
       </c>
       <c r="AD2">
         <v>1521441.9</v>
@@ -779,10 +779,10 @@
         <v>0.09338793455917278</v>
       </c>
       <c r="X3">
-        <v>0.1345323738216071</v>
+        <v>0.1344931977877493</v>
       </c>
       <c r="Y3">
-        <v>-0.04114443926243434</v>
+        <v>-0.04110526322857654</v>
       </c>
       <c r="Z3">
         <v>1.32194904946109</v>
@@ -791,10 +791,10 @@
         <v>0.003805010149987582</v>
       </c>
       <c r="AB3">
-        <v>0.05918006114963659</v>
+        <v>0.05917321121135413</v>
       </c>
       <c r="AC3">
-        <v>-0.055375050999649</v>
+        <v>-0.05536820106136655</v>
       </c>
       <c r="AD3">
         <v>643332</v>
@@ -910,10 +910,10 @@
         <v>0.09028991903976892</v>
       </c>
       <c r="X4">
-        <v>0.1744773465414663</v>
+        <v>0.1744205344911657</v>
       </c>
       <c r="Y4">
-        <v>-0.08418742750169735</v>
+        <v>-0.08413061545139679</v>
       </c>
       <c r="Z4">
         <v>0.487071046933657</v>
@@ -922,10 +922,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05866937064032381</v>
+        <v>0.05866268095382822</v>
       </c>
       <c r="AC4">
-        <v>-0.05866937064032381</v>
+        <v>-0.05866268095382822</v>
       </c>
       <c r="AD4">
         <v>466786.2</v>
@@ -1035,10 +1035,10 @@
         <v>0.07576781504859513</v>
       </c>
       <c r="X5">
-        <v>0.1287360554536813</v>
+        <v>0.1286994385395095</v>
       </c>
       <c r="Y5">
-        <v>-0.05296824040508614</v>
+        <v>-0.05293162349091433</v>
       </c>
       <c r="Z5">
         <v>0.5435131885952269</v>
@@ -1047,10 +1047,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05929842963108367</v>
+        <v>0.05929154254944274</v>
       </c>
       <c r="AC5">
-        <v>-0.05929842963108367</v>
+        <v>-0.05929154254944274</v>
       </c>
       <c r="AD5">
         <v>403434.7</v>
@@ -1157,10 +1157,10 @@
         <v>-0.1220168419581397</v>
       </c>
       <c r="X6">
-        <v>0.1185283131244147</v>
+        <v>0.1184962030079525</v>
       </c>
       <c r="Y6">
-        <v>-0.2405451550825544</v>
+        <v>-0.2405130449660922</v>
       </c>
       <c r="Z6">
         <v>0.3372015361496078</v>
@@ -1169,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06091524320838732</v>
+        <v>0.06090827494183532</v>
       </c>
       <c r="AC6">
-        <v>-0.06091524320838732</v>
+        <v>-0.06090827494183532</v>
       </c>
       <c r="AD6">
         <v>7889</v>
